--- a/data/nzd0052/nzd0052.xlsx
+++ b/data/nzd0052/nzd0052.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E501"/>
+  <dimension ref="A1:E503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10953,6 +10953,48 @@
         <v>386.82</v>
       </c>
       <c r="E501" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>378.94</v>
+      </c>
+      <c r="C502" t="n">
+        <v>382.57</v>
+      </c>
+      <c r="D502" t="n">
+        <v>386.13</v>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>377.55</v>
+      </c>
+      <c r="C503" t="n">
+        <v>381.51</v>
+      </c>
+      <c r="D503" t="n">
+        <v>385.51</v>
+      </c>
+      <c r="E503" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -10969,7 +11011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B594"/>
+  <dimension ref="A1:B597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16912,6 +16954,36 @@
       </c>
       <c r="B594" t="n">
         <v>0.65</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="n">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -17080,28 +17152,28 @@
         <v>0.0864</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05385291823222173</v>
+        <v>0.05305266420040152</v>
       </c>
       <c r="J2" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K2" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01515248316682594</v>
+        <v>0.0148223288769177</v>
       </c>
       <c r="M2" t="n">
-        <v>2.560770369833242</v>
+        <v>2.554935982640405</v>
       </c>
       <c r="N2" t="n">
-        <v>11.16639259390189</v>
+        <v>11.12848136104928</v>
       </c>
       <c r="O2" t="n">
-        <v>3.341615267187695</v>
+        <v>3.335937853295424</v>
       </c>
       <c r="P2" t="n">
-        <v>377.9139947402781</v>
+        <v>377.921926715113</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17158,28 +17230,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1875864539872963</v>
+        <v>0.1852696757028458</v>
       </c>
       <c r="J3" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K3" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1634606559561467</v>
+        <v>0.1606839491328064</v>
       </c>
       <c r="M3" t="n">
-        <v>2.557191883082608</v>
+        <v>2.559345876377441</v>
       </c>
       <c r="N3" t="n">
-        <v>10.66805647923207</v>
+        <v>10.66559542598806</v>
       </c>
       <c r="O3" t="n">
-        <v>3.266199087507077</v>
+        <v>3.265822320027232</v>
       </c>
       <c r="P3" t="n">
-        <v>380.2457671457709</v>
+        <v>380.2687247400928</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17236,28 +17308,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.001541401762341871</v>
+        <v>-0.002610311843297704</v>
       </c>
       <c r="J4" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K4" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L4" t="n">
-        <v>1.230059983725607e-05</v>
+        <v>3.55375358016552e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>2.683010430908293</v>
+        <v>2.678386801183367</v>
       </c>
       <c r="N4" t="n">
-        <v>11.44219367419915</v>
+        <v>11.40526642607831</v>
       </c>
       <c r="O4" t="n">
-        <v>3.382631176199845</v>
+        <v>3.377168403571002</v>
       </c>
       <c r="P4" t="n">
-        <v>387.3125913837729</v>
+        <v>387.3231837536986</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17295,7 +17367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E501"/>
+  <dimension ref="A1:E503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30825,6 +30897,60 @@
         </is>
       </c>
     </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>-35.020460964337,173.86253878919013</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>-35.020859327357165,173.86326283432734</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>-35.02110551322447,173.86407694919433</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>-35.020471082602974,173.86252979854618</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>-35.02086765103212,173.86325712408274</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>-35.02111067146935,173.86407432939552</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0052/nzd0052.xlsx
+++ b/data/nzd0052/nzd0052.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E503"/>
+  <dimension ref="A1:E505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10997,6 +10997,48 @@
       <c r="E503" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>377.29</v>
+      </c>
+      <c r="C504" t="n">
+        <v>381.3</v>
+      </c>
+      <c r="D504" t="n">
+        <v>385.79</v>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:33+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>376.9</v>
+      </c>
+      <c r="C505" t="n">
+        <v>379.14</v>
+      </c>
+      <c r="D505" t="n">
+        <v>383.97</v>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11011,7 +11053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B597"/>
+  <dimension ref="A1:B599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16984,6 +17026,26 @@
       </c>
       <c r="B597" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="n">
+        <v>-0.03</v>
       </c>
     </row>
   </sheetData>
@@ -17152,28 +17214,28 @@
         <v>0.0864</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05305266420040152</v>
+        <v>0.05141916268306773</v>
       </c>
       <c r="J2" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K2" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0148223288769177</v>
+        <v>0.01402445005129738</v>
       </c>
       <c r="M2" t="n">
-        <v>2.554935982640405</v>
+        <v>2.553674619016565</v>
       </c>
       <c r="N2" t="n">
-        <v>11.12848136104928</v>
+        <v>11.10390007702276</v>
       </c>
       <c r="O2" t="n">
-        <v>3.335937853295424</v>
+        <v>3.332251502666442</v>
       </c>
       <c r="P2" t="n">
-        <v>377.921926715113</v>
+        <v>377.9381847878525</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17230,28 +17292,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1852696757028458</v>
+        <v>0.1816410211940469</v>
       </c>
       <c r="J3" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K3" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1606839491328064</v>
+        <v>0.1552568360572781</v>
       </c>
       <c r="M3" t="n">
-        <v>2.559345876377441</v>
+        <v>2.568588450871767</v>
       </c>
       <c r="N3" t="n">
-        <v>10.66559542598806</v>
+        <v>10.72375943887893</v>
       </c>
       <c r="O3" t="n">
-        <v>3.265822320027232</v>
+        <v>3.274715169122183</v>
       </c>
       <c r="P3" t="n">
-        <v>380.2687247400928</v>
+        <v>380.3048429029323</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17308,28 +17370,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.002610311843297704</v>
+        <v>-0.004355605735325793</v>
       </c>
       <c r="J4" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K4" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L4" t="n">
-        <v>3.55375358016552e-05</v>
+        <v>9.952883989572392e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>2.678386801183367</v>
+        <v>2.677543441238154</v>
       </c>
       <c r="N4" t="n">
-        <v>11.40526642607831</v>
+        <v>11.38544977982043</v>
       </c>
       <c r="O4" t="n">
-        <v>3.377168403571002</v>
+        <v>3.37423321360875</v>
       </c>
       <c r="P4" t="n">
-        <v>387.3231837536986</v>
+        <v>387.3405572316421</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17367,7 +17429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E503"/>
+  <dimension ref="A1:E505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30951,6 +31013,60 @@
         </is>
       </c>
     </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>-35.02047297522819,173.86252811684273</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>-35.02086930006202,173.8632559928077</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>-35.0211083419394,173.8640755125305</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:33+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>-35.020475814165984,173.86252559428743</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>-35.020886261511926,173.86324435683352</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>-35.02112348388381,173.8640678221519</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0052/nzd0052.xlsx
+++ b/data/nzd0052/nzd0052.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E505"/>
+  <dimension ref="A1:E506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11037,6 +11037,27 @@
         <v>383.97</v>
       </c>
       <c r="E505" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>375.18</v>
+      </c>
+      <c r="C506" t="n">
+        <v>375.28</v>
+      </c>
+      <c r="D506" t="n">
+        <v>381.08</v>
+      </c>
+      <c r="E506" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11053,7 +11074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B599"/>
+  <dimension ref="A1:B600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17046,6 +17067,16 @@
       </c>
       <c r="B599" t="n">
         <v>-0.03</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="n">
+        <v>0.06</v>
       </c>
     </row>
   </sheetData>
@@ -17214,28 +17245,28 @@
         <v>0.0864</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05141916268306773</v>
+        <v>0.04989853200860801</v>
       </c>
       <c r="J2" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K2" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01402445005129738</v>
+        <v>0.01323242813368752</v>
       </c>
       <c r="M2" t="n">
-        <v>2.553674619016565</v>
+        <v>2.556804318364093</v>
       </c>
       <c r="N2" t="n">
-        <v>11.10390007702276</v>
+        <v>11.11541830535711</v>
       </c>
       <c r="O2" t="n">
-        <v>3.332251502666442</v>
+        <v>3.333979349869629</v>
       </c>
       <c r="P2" t="n">
-        <v>377.9381847878525</v>
+        <v>377.9534054648656</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17292,28 +17323,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1816410211940469</v>
+        <v>0.178012860709736</v>
       </c>
       <c r="J3" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K3" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1552568360572781</v>
+        <v>0.148318910787032</v>
       </c>
       <c r="M3" t="n">
-        <v>2.568588450871767</v>
+        <v>2.583037770170103</v>
       </c>
       <c r="N3" t="n">
-        <v>10.72375943887893</v>
+        <v>10.89326788401385</v>
       </c>
       <c r="O3" t="n">
-        <v>3.274715169122183</v>
+        <v>3.300495096801971</v>
       </c>
       <c r="P3" t="n">
-        <v>380.3048429029323</v>
+        <v>380.3411587946281</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17370,28 +17401,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.004355605735325793</v>
+        <v>-0.006618647621731538</v>
       </c>
       <c r="J4" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K4" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L4" t="n">
-        <v>9.952883989572392e-05</v>
+        <v>0.0002292437138976533</v>
       </c>
       <c r="M4" t="n">
-        <v>2.677543441238154</v>
+        <v>2.68477856222451</v>
       </c>
       <c r="N4" t="n">
-        <v>11.38544977982043</v>
+        <v>11.43711429683385</v>
       </c>
       <c r="O4" t="n">
-        <v>3.37423321360875</v>
+        <v>3.381880290139474</v>
       </c>
       <c r="P4" t="n">
-        <v>387.3405572316421</v>
+        <v>387.3632090367111</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17429,7 +17460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E505"/>
+  <dimension ref="A1:E506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31067,6 +31098,33 @@
         </is>
       </c>
     </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>-35.020488334608956,173.86251446916972</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>-35.02091657224838,173.86322356290484</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>-35.021147527959386,173.86405561050105</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0052/nzd0052.xlsx
+++ b/data/nzd0052/nzd0052.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E506"/>
+  <dimension ref="A1:E510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11060,6 +11060,90 @@
       <c r="E506" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>375.42</v>
+      </c>
+      <c r="C507" t="n">
+        <v>374.85</v>
+      </c>
+      <c r="D507" t="n">
+        <v>381.13</v>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:17:10+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>374.31</v>
+      </c>
+      <c r="C508" t="n">
+        <v>375.12</v>
+      </c>
+      <c r="D508" t="n">
+        <v>381.52</v>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>374.71</v>
+      </c>
+      <c r="C509" t="n">
+        <v>376.12</v>
+      </c>
+      <c r="D509" t="n">
+        <v>382.31</v>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>374.47</v>
+      </c>
+      <c r="C510" t="n">
+        <v>377.45</v>
+      </c>
+      <c r="D510" t="n">
+        <v>382.43</v>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11074,7 +11158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B600"/>
+  <dimension ref="A1:B604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17077,6 +17161,46 @@
       </c>
       <c r="B600" t="n">
         <v>0.06</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B603" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B604" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -17245,28 +17369,28 @@
         <v>0.0864</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04989853200860801</v>
+        <v>0.0432650121313904</v>
       </c>
       <c r="J2" t="n">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="K2" t="n">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01323242813368752</v>
+        <v>0.01000118285296681</v>
       </c>
       <c r="M2" t="n">
-        <v>2.556804318364093</v>
+        <v>2.572190675966926</v>
       </c>
       <c r="N2" t="n">
-        <v>11.11541830535711</v>
+        <v>11.18883582108067</v>
       </c>
       <c r="O2" t="n">
-        <v>3.333979349869629</v>
+        <v>3.3449717220151</v>
       </c>
       <c r="P2" t="n">
-        <v>377.9534054648656</v>
+        <v>378.0202101874487</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17323,28 +17447,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.178012860709736</v>
+        <v>0.1646325317214872</v>
       </c>
       <c r="J3" t="n">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="K3" t="n">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="L3" t="n">
-        <v>0.148318910787032</v>
+        <v>0.1249243058882724</v>
       </c>
       <c r="M3" t="n">
-        <v>2.583037770170103</v>
+        <v>2.636386296697867</v>
       </c>
       <c r="N3" t="n">
-        <v>10.89326788401385</v>
+        <v>11.46457403721347</v>
       </c>
       <c r="O3" t="n">
-        <v>3.300495096801971</v>
+        <v>3.385937689505444</v>
       </c>
       <c r="P3" t="n">
-        <v>380.3411587946281</v>
+        <v>380.4758824044017</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17401,28 +17525,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.006618647621731538</v>
+        <v>-0.01438284259221393</v>
       </c>
       <c r="J4" t="n">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="K4" t="n">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002292437138976533</v>
+        <v>0.001078673065018632</v>
       </c>
       <c r="M4" t="n">
-        <v>2.68477856222451</v>
+        <v>2.7058983752853</v>
       </c>
       <c r="N4" t="n">
-        <v>11.43711429683385</v>
+        <v>11.56801490773117</v>
       </c>
       <c r="O4" t="n">
-        <v>3.381880290139474</v>
+        <v>3.401178458671519</v>
       </c>
       <c r="P4" t="n">
-        <v>387.3632090367111</v>
+        <v>387.4413851575051</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17460,7 +17584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E506"/>
+  <dimension ref="A1:E510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31125,6 +31249,114 @@
         </is>
       </c>
     </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>-35.02048658757045,173.8625160215119</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>-35.02091994883279,173.86322124648177</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>-35.021147111971935,173.86405582177537</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:17:10+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>-35.02049466762332,173.86250884192867</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>-35.02091782865189,173.86322270098</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>-35.02114386726974,173.8640574697148</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>-35.020491755892614,173.86251142916603</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>-35.02090997612987,173.86322808800978</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>-35.02113729466786,173.86406080784815</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>-35.020493502931046,173.86250987682362</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>-35.0208995322752,173.86323525275782</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>-35.02113629629794,173.8640613149063</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0052/nzd0052.xlsx
+++ b/data/nzd0052/nzd0052.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E510"/>
+  <dimension ref="A1:E513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11142,6 +11142,69 @@
         <v>382.43</v>
       </c>
       <c r="E510" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>374.34</v>
+      </c>
+      <c r="C511" t="n">
+        <v>377.69</v>
+      </c>
+      <c r="D511" t="n">
+        <v>383.16</v>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>373.78</v>
+      </c>
+      <c r="C512" t="n">
+        <v>377.57</v>
+      </c>
+      <c r="D512" t="n">
+        <v>382.55</v>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>374.95</v>
+      </c>
+      <c r="C513" t="n">
+        <v>378.79</v>
+      </c>
+      <c r="D513" t="n">
+        <v>383.76</v>
+      </c>
+      <c r="E513" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11158,7 +11221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B604"/>
+  <dimension ref="A1:B607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17201,6 +17264,36 @@
       </c>
       <c r="B604" t="n">
         <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B605" t="n">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B607" t="n">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
@@ -17369,28 +17462,28 @@
         <v>0.0864</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0432650121313904</v>
+        <v>0.03806571207811689</v>
       </c>
       <c r="J2" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="K2" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01000118285296681</v>
+        <v>0.007760479966122391</v>
       </c>
       <c r="M2" t="n">
-        <v>2.572190675966926</v>
+        <v>2.584999693186121</v>
       </c>
       <c r="N2" t="n">
-        <v>11.18883582108067</v>
+        <v>11.25834958062822</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3449717220151</v>
+        <v>3.355346417380509</v>
       </c>
       <c r="P2" t="n">
-        <v>378.0202101874487</v>
+        <v>378.0727443939113</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17447,28 +17540,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1646325317214872</v>
+        <v>0.1572385735882719</v>
       </c>
       <c r="J3" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="K3" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1249243058882724</v>
+        <v>0.1140625450089647</v>
       </c>
       <c r="M3" t="n">
-        <v>2.636386296697867</v>
+        <v>2.663448915739537</v>
       </c>
       <c r="N3" t="n">
-        <v>11.46457403721347</v>
+        <v>11.66962957597929</v>
       </c>
       <c r="O3" t="n">
-        <v>3.385937689505444</v>
+        <v>3.416083953297883</v>
       </c>
       <c r="P3" t="n">
-        <v>380.4758824044017</v>
+        <v>380.5505906483432</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17525,28 +17618,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01438284259221393</v>
+        <v>-0.01858573503975539</v>
       </c>
       <c r="J4" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="K4" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001078673065018632</v>
+        <v>0.001808024960082477</v>
       </c>
       <c r="M4" t="n">
-        <v>2.7058983752853</v>
+        <v>2.712751641599462</v>
       </c>
       <c r="N4" t="n">
-        <v>11.56801490773117</v>
+        <v>11.58905462366207</v>
       </c>
       <c r="O4" t="n">
-        <v>3.401178458671519</v>
+        <v>3.404270057392931</v>
       </c>
       <c r="P4" t="n">
-        <v>387.4413851575051</v>
+        <v>387.4838511574516</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17584,7 +17677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E510"/>
+  <dimension ref="A1:E513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31357,6 +31450,87 @@
         </is>
       </c>
     </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>-35.02049444924353,173.86250903597147</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>-35.020897647669806,173.86323654564447</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>-35.02113022288089,173.86406439951</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>-35.02049852566645,173.86250541383885</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>-35.020898589972504,173.86323589920116</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>-35.02113529792801,173.8640618219645</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>-35.020490008854146,173.86251298150836</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>-35.0208890098949,173.8632424713743</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>-35.02112523103121,173.86406693480035</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0052/nzd0052.xlsx
+++ b/data/nzd0052/nzd0052.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E513"/>
+  <dimension ref="A1:E518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11205,6 +11205,111 @@
         <v>383.76</v>
       </c>
       <c r="E513" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>372.92</v>
+      </c>
+      <c r="C514" t="n">
+        <v>376.71</v>
+      </c>
+      <c r="D514" t="n">
+        <v>382.4</v>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>373.69</v>
+      </c>
+      <c r="C515" t="n">
+        <v>377.65</v>
+      </c>
+      <c r="D515" t="n">
+        <v>383.3</v>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>374.95</v>
+      </c>
+      <c r="C516" t="n">
+        <v>378.47</v>
+      </c>
+      <c r="D516" t="n">
+        <v>384.35</v>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>378.2</v>
+      </c>
+      <c r="C517" t="n">
+        <v>378.92</v>
+      </c>
+      <c r="D517" t="n">
+        <v>384.81</v>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>378.71</v>
+      </c>
+      <c r="C518" t="n">
+        <v>379.22</v>
+      </c>
+      <c r="D518" t="n">
+        <v>385.31</v>
+      </c>
+      <c r="E518" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11221,7 +11326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B607"/>
+  <dimension ref="A1:B612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17294,6 +17399,56 @@
       </c>
       <c r="B607" t="n">
         <v>0.05</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B608" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
@@ -17462,28 +17617,28 @@
         <v>0.0864</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03806571207811689</v>
+        <v>0.03209362907067859</v>
       </c>
       <c r="J2" t="n">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="K2" t="n">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007760479966122391</v>
+        <v>0.005559897911511236</v>
       </c>
       <c r="M2" t="n">
-        <v>2.584999693186121</v>
+        <v>2.592706866234189</v>
       </c>
       <c r="N2" t="n">
-        <v>11.25834958062822</v>
+        <v>11.31126975221744</v>
       </c>
       <c r="O2" t="n">
-        <v>3.355346417380509</v>
+        <v>3.363223119600816</v>
       </c>
       <c r="P2" t="n">
-        <v>378.0727443939113</v>
+        <v>378.1333224542484</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17540,28 +17695,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1572385735882719</v>
+        <v>0.1456771564905306</v>
       </c>
       <c r="J3" t="n">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="K3" t="n">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1140625450089647</v>
+        <v>0.09816651510255481</v>
       </c>
       <c r="M3" t="n">
-        <v>2.663448915739537</v>
+        <v>2.705633088155755</v>
       </c>
       <c r="N3" t="n">
-        <v>11.66962957597929</v>
+        <v>11.97037577265251</v>
       </c>
       <c r="O3" t="n">
-        <v>3.416083953297883</v>
+        <v>3.459823084010584</v>
       </c>
       <c r="P3" t="n">
-        <v>380.5505906483432</v>
+        <v>380.6679125973878</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17618,28 +17773,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01858573503975539</v>
+        <v>-0.02377648891161131</v>
       </c>
       <c r="J4" t="n">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="K4" t="n">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001808024960082477</v>
+        <v>0.002991169375655245</v>
       </c>
       <c r="M4" t="n">
-        <v>2.712751641599462</v>
+        <v>2.714074118246261</v>
       </c>
       <c r="N4" t="n">
-        <v>11.58905462366207</v>
+        <v>11.56951980631742</v>
       </c>
       <c r="O4" t="n">
-        <v>3.404270057392931</v>
+        <v>3.401399683412318</v>
       </c>
       <c r="P4" t="n">
-        <v>387.4838511574516</v>
+        <v>387.5365169306961</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17677,7 +17832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E513"/>
+  <dimension ref="A1:E518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31531,6 +31686,141 @@
         </is>
       </c>
     </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>-35.02050478588714,173.86249985127736</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>-35.02090534314175,173.86323126635688</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>-35.021136545890414,173.86406118814176</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>-35.02049918080582,173.86250483171037</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>-35.02089796177071,173.86323633016337</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>-35.02112905811597,173.86406499107778</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>-35.020490008854146,173.86251298150836</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>-35.02089152270217,173.86324074752577</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>-35.021120322378984,173.86406942783557</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>-35.02046635103983,173.8625340028044</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>-35.02088798906694,173.86324317168774</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>-35.02111649529415,173.86407137155777</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>-35.02046263858249,173.86253730152976</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>-35.02088563331009,173.86324478779562</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>-35.021112335419296,173.86407348429907</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
